--- a/output/pdf_financials_xlsx/NPT.xlsx
+++ b/output/pdf_financials_xlsx/NPT.xlsx
@@ -5889,7 +5889,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">

--- a/output/pdf_financials_xlsx/NPT.xlsx
+++ b/output/pdf_financials_xlsx/NPT.xlsx
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>1310.561</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>1317.509</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>1514.7</v>
       </c>
     </row>
     <row r="29">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2254.198</v>
+        <v>-943.6369999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1071.906</v>
+        <v>2389.415</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1789.375</v>
+        <v>-274.675</v>
       </c>
     </row>
     <row r="30">
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-11.30313611912278</v>
+        <v>-4.731641789248623</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>4.428484344327501</v>
+        <v>9.871655648537553</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-7.503503032536949</v>
+        <v>-1.151812613600887</v>
       </c>
     </row>
     <row r="31">
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>1310.561</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1317.509</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>1514.7</v>
       </c>
     </row>
     <row r="101">
@@ -4694,7 +4694,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="n">
         <v>1310.561</v>
       </c>

--- a/output/pdf_financials_xlsx/NPT.xlsx
+++ b/output/pdf_financials_xlsx/NPT.xlsx
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>252.09</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>462.77</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>274.902</v>
       </c>
     </row>
     <row r="68">
@@ -1530,13 +1530,13 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>2070.944</v>
+        <v>2323.034</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>2266.957</v>
+        <v>2729.727</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>2591.531</v>
+        <v>2866.433</v>
       </c>
     </row>
     <row r="69">
@@ -1642,13 +1642,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>6075.459</v>
+        <v>5823.369</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>3566.163</v>
+        <v>3103.393</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>5812.961</v>
+        <v>5538.059</v>
       </c>
     </row>
     <row r="76">
